--- a/htr-Corps-ModeleMetier/ig/StructureDefinition-FrActeSubstitution.xlsx
+++ b/htr-Corps-ModeleMetier/ig/StructureDefinition-FrActeSubstitution.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-27T14:36:02+00:00</t>
+    <t>2025-06-05T15:38:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-Corps-ModeleMetier/ig/StructureDefinition-FrActeSubstitution.xlsx
+++ b/htr-Corps-ModeleMetier/ig/StructureDefinition-FrActeSubstitution.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-06-05T15:38:56+00:00</t>
+    <t>2025-10-06T12:29:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -4429,7 +4429,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="33" hidden="true">
+    <row r="33">
       <c r="A33" t="s" s="2">
         <v>157</v>
       </c>
@@ -5754,7 +5754,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="46" hidden="true">
+    <row r="46">
       <c r="A46" t="s" s="2">
         <v>209</v>
       </c>
@@ -8364,12 +8364,12 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:AK71">
-    <filterColumn colId="6">
+    <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
       </customFilters>
     </filterColumn>
-    <filterColumn colId="26">
+    <filterColumn colId="27">
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
